--- a/Jens_locations.xlsx
+++ b/Jens_locations.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wageningenur4-my.sharepoint.com/personal/ward_koehler_wur_nl/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wardk\Documents\MSc Biology\MSc Thesis\Pelargonium_thesis_depository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{D603BE02-6521-45C3-8E06-7F615D4A7117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7CEA5ED-7634-4E42-B0CA-21D96B3FD361}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F91D527-E2C7-4245-B8ED-2E754622E657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1956" yWindow="1776" windowWidth="17280" windowHeight="8976" xr2:uid="{EA5EF1A7-04F9-4576-A390-E32A8FCD74A4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EA5EF1A7-04F9-4576-A390-E32A8FCD74A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
   <si>
     <t>Number</t>
   </si>
@@ -160,6 +159,45 @@
   </si>
   <si>
     <t>CaTo</t>
+  </si>
+  <si>
+    <t>Helderberg</t>
+  </si>
+  <si>
+    <t>West Coast NP</t>
+  </si>
+  <si>
+    <t>Elandsberg</t>
+  </si>
+  <si>
+    <t>Ijzerfontein</t>
+  </si>
+  <si>
+    <t>Darling</t>
+  </si>
+  <si>
+    <t>Silwerstroomstrand</t>
+  </si>
+  <si>
+    <t>Leeurivier</t>
+  </si>
+  <si>
+    <t>Romansrivier</t>
+  </si>
+  <si>
+    <t>Paarl mountain</t>
+  </si>
+  <si>
+    <t>Constanziaberg</t>
+  </si>
+  <si>
+    <t>Pringle Bay</t>
+  </si>
+  <si>
+    <t>Fig.1.4_match</t>
+  </si>
+  <si>
+    <t>Fig.1.4._no_match</t>
   </si>
 </sst>
 </file>
@@ -531,13 +569,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70E6B3B-0544-43C6-B29F-A6A8D472137F}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -547,8 +585,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -558,8 +602,14 @@
       <c r="C2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -569,8 +619,11 @@
       <c r="C3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -580,8 +633,11 @@
       <c r="C4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -591,8 +647,11 @@
       <c r="C5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -602,8 +661,14 @@
       <c r="C6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -613,8 +678,14 @@
       <c r="C7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -624,8 +695,14 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -635,8 +712,14 @@
       <c r="C9" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -647,7 +730,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -657,8 +740,11 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -669,7 +755,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -679,8 +765,11 @@
       <c r="C13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -690,8 +779,11 @@
       <c r="C14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -701,8 +793,11 @@
       <c r="C15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -712,8 +807,11 @@
       <c r="C16" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -724,7 +822,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -734,8 +832,11 @@
       <c r="C18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -745,8 +846,11 @@
       <c r="C19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
